--- a/onderzoek_meta.xlsx
+++ b/onderzoek_meta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_47F1CC4B14E253851DB2A8B845C3C6C5FF9A1485" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFCA8A17-B74E-4EAB-BD10-9B3E9BD84FC9}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_47F1CC4B14E253851DB2A8B845C3C6C5FF9A1485" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245E8998-D85C-4A92-A122-3531FEC35F4A}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SA" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="23">
   <si>
     <t>Snelheidsverhoging (%)</t>
   </si>
@@ -84,6 +84,15 @@
   <si>
     <t>M1 + M2 + M3</t>
   </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
 </sst>
 </file>
 
@@ -135,6 +144,1056 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA Improved'!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M1 M2 M3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA Improved'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA Improved'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>737.36111111111086</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>324.28282828282818</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310.50000000000011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>307.30769230769232</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>158</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E9CC-4356-9848-91E4C7CF2B3D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA Improved'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA Improved'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>737.36111111111086</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550.04545454545462</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>209.86111111111109</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>542.96581196581167</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>213.55555555555549</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E9CC-4356-9848-91E4C7CF2B3D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA Improved'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA Improved'!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>737.36111111111086</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>278.06818181818193</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>179.73148148148161</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>498.55982905982899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>158.888888888889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E9CC-4356-9848-91E4C7CF2B3D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1794488576"/>
+        <c:axId val="1794484256"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1794488576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1794484256"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1794484256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1794488576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>117475</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>511175</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3EA908B-DD14-3C30-55AB-EBC6A653CF30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,13 +1482,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +1502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -457,7 +1516,7 @@
         <v>737.36111111111109</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10</v>
       </c>
@@ -471,7 +1530,7 @@
         <v>289.25000000000011</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20</v>
       </c>
@@ -485,7 +1544,7 @@
         <v>256.527777777778</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>30</v>
       </c>
@@ -499,7 +1558,7 @@
         <v>498.55982905982899</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50</v>
       </c>
@@ -521,27 +1580,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -555,7 +1614,7 @@
         <v>737.36111111111086</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10</v>
       </c>
@@ -569,7 +1628,7 @@
         <v>278.06818181818193</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20</v>
       </c>
@@ -583,7 +1642,7 @@
         <v>179.73148148148161</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>30</v>
       </c>
@@ -597,7 +1656,7 @@
         <v>498.55982905982899</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50</v>
       </c>
@@ -613,26 +1672,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K114"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -667,7 +1727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -696,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -731,7 +1791,7 @@
         <v>61.656877686261723</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -766,7 +1826,7 @@
         <v>62.733608452199498</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -801,7 +1861,7 @@
         <v>57.439471434574124</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -836,7 +1896,7 @@
         <v>47.133341324337742</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -871,7 +1931,7 @@
         <v>74.454357095155729</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -906,7 +1966,7 @@
         <v>85.228856658504426</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -941,7 +2001,7 @@
         <v>79.565614268948224</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -976,7 +2036,7 @@
         <v>93.151252589941606</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1011,7 +2071,7 @@
         <v>33.068506178319673</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1046,7 +2106,7 @@
         <v>81.906197023921621</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1081,7 +2141,7 @@
         <v>81.043511019024308</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1116,7 +2176,7 @@
         <v>87.488299984061896</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1151,7 +2211,7 @@
         <v>81.070908748437489</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1186,7 +2246,7 @@
         <v>73.659822942173676</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1221,7 +2281,7 @@
         <v>81.30489589521423</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1256,7 +2316,7 @@
         <v>94.477302693539272</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1291,7 +2351,7 @@
         <v>49.444339800339023</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1326,7 +2386,7 @@
         <v>86.680593845784998</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1361,7 +2421,7 @@
         <v>82.079672070254119</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1396,7 +2456,7 @@
         <v>75.158478741074333</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -1431,7 +2491,7 @@
         <v>58.765047346701138</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1466,7 +2526,7 @@
         <v>84.675080052740626</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1501,7 +2561,7 @@
         <v>73.084892128026425</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1536,7 +2596,7 @@
         <v>91.584102467508004</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1571,7 +2631,7 @@
         <v>72.834519031542953</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1606,7 +2666,7 @@
         <v>76.181327305832866</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1641,7 +2701,7 @@
         <v>94.269238013822672</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1676,7 +2736,7 @@
         <v>97.689458152822255</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1711,7 +2771,7 @@
         <v>72.366650113871799</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1746,7 +2806,7 @@
         <v>85.891881710303238</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1781,7 +2841,7 @@
         <v>86.709361461668848</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1816,7 +2876,7 @@
         <v>98.915049915238271</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -1851,7 +2911,7 @@
         <v>57.884895289302882</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -1886,7 +2946,7 @@
         <v>66.822719567115854</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -1921,7 +2981,7 @@
         <v>78.073807902400873</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -1956,7 +3016,7 @@
         <v>70.497440024657962</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1991,7 +3051,7 @@
         <v>72.924878850665237</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -2026,7 +3086,7 @@
         <v>77.143215922647045</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -2061,7 +3121,7 @@
         <v>80.945564136372198</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -2096,7 +3156,7 @@
         <v>82.570477804985245</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2131,7 +3191,7 @@
         <v>71.907211266789346</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -2166,7 +3226,7 @@
         <v>80.834287204601736</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -2201,7 +3261,7 @@
         <v>76.402335656432456</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2236,7 +3296,7 @@
         <v>85.96345827839518</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -2271,7 +3331,7 @@
         <v>96.865699755132795</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -2306,7 +3366,7 @@
         <v>78.524518113894629</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -2341,7 +3401,7 @@
         <v>92.142225828419072</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -2376,7 +3436,7 @@
         <v>82.678470521755514</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -2411,7 +3471,7 @@
         <v>77.539341427079236</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -2446,7 +3506,7 @@
         <v>57.494705959576919</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -2481,7 +3541,7 @@
         <v>80.544872343704498</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -2516,7 +3576,7 @@
         <v>74.366684361033563</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -2551,7 +3611,7 @@
         <v>56.842069213513923</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -2586,7 +3646,7 @@
         <v>76.492748163495932</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -2621,7 +3681,7 @@
         <v>84.224387403893914</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -2656,7 +3716,7 @@
         <v>95.920135618760597</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -2691,7 +3751,7 @@
         <v>77.293710245301881</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -2726,7 +3786,7 @@
         <v>80.898057176075625</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -2761,7 +3821,7 @@
         <v>77.184751582943335</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -2796,7 +3856,7 @@
         <v>79.943492183085311</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -2831,7 +3891,7 @@
         <v>75.859860614051598</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -2866,7 +3926,7 @@
         <v>91.246425452490627</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -2901,7 +3961,7 @@
         <v>92.779749916687209</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -2936,7 +3996,7 @@
         <v>83.310673127964506</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -2971,7 +4031,7 @@
         <v>90.588879946574423</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>19</v>
       </c>
@@ -3006,7 +4066,7 @@
         <v>69.929622082569892</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -3041,7 +4101,7 @@
         <v>82.856397699117608</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -3076,7 +4136,7 @@
         <v>83.962739087998088</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -3111,7 +4171,7 @@
         <v>77.75235877326665</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>19</v>
       </c>
@@ -3146,7 +4206,7 @@
         <v>92.232058768129562</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -3181,7 +4241,7 @@
         <v>67.76098642363479</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -3216,7 +4276,7 @@
         <v>87.839517799962323</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -3251,7 +4311,7 @@
         <v>82.144688989669206</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -3286,7 +4346,7 @@
         <v>78.679648975373183</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>19</v>
       </c>
@@ -3321,7 +4381,7 @@
         <v>94.832577480910516</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -3356,7 +4416,7 @@
         <v>97.21981540779808</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -3391,7 +4451,7 @@
         <v>86.228188838849974</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>19</v>
       </c>
@@ -3426,7 +4486,7 @@
         <v>97.609091479876923</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>19</v>
       </c>
@@ -3461,7 +4521,7 @@
         <v>92.473158786965527</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -3496,7 +4556,7 @@
         <v>96.202674703333955</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>19</v>
       </c>
@@ -3531,7 +4591,7 @@
         <v>89.664944210056305</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>19</v>
       </c>
@@ -3566,7 +4626,7 @@
         <v>74.931534215768508</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>19</v>
       </c>
@@ -3601,7 +4661,7 @@
         <v>99.963013065292216</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>19</v>
       </c>
@@ -3636,7 +4696,7 @@
         <v>66.660388020342808</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -3671,7 +4731,7 @@
         <v>68.240130560718242</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>19</v>
       </c>
@@ -3706,7 +4766,7 @@
         <v>95.071842203128682</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>19</v>
       </c>
@@ -3741,7 +4801,7 @@
         <v>82.057464103047067</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>19</v>
       </c>
@@ -3776,7 +4836,7 @@
         <v>91.925467638407923</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -3811,7 +4871,7 @@
         <v>85.073032072466987</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -3846,7 +4906,7 @@
         <v>91.321558456612124</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -3881,7 +4941,7 @@
         <v>87.481345175826235</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -3916,7 +4976,7 @@
         <v>93.440456699074133</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -3951,7 +5011,7 @@
         <v>88.291580335279718</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3986,7 +5046,7 @@
         <v>89.858730457713293</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -4021,7 +5081,7 @@
         <v>82.849442890881946</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -4056,7 +5116,7 @@
         <v>99.639122728216734</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -4091,7 +5151,7 @@
         <v>70.130995393756734</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -4126,7 +5186,7 @@
         <v>90.568331649514548</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -4161,7 +5221,7 @@
         <v>84.031760290942799</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -4196,7 +5256,7 @@
         <v>97.689458152822255</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -4231,7 +5291,7 @@
         <v>78.111953971814586</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -4266,7 +5326,7 @@
         <v>96.880768506310034</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -4301,7 +5361,7 @@
         <v>81.013373516669802</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -4336,7 +5396,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -4371,7 +5431,7 @@
         <v>82.731421902640605</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -4406,7 +5466,7 @@
         <v>88.246374081747959</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>19</v>
       </c>
@@ -4441,7 +5501,7 @@
         <v>70.330788066708195</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -4476,7 +5536,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -4511,7 +5571,7 @@
         <v>92.766999434921829</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>19</v>
       </c>
@@ -4546,7 +5606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>19</v>
       </c>
@@ -4581,7 +5641,7 @@
         <v>92.405349406667924</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -4624,20 +5684,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -4672,7 +5732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -4707,7 +5767,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -4742,7 +5802,7 @@
         <v>98.915049915238271</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4777,7 +5837,7 @@
         <v>96.865699755132795</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4812,7 +5872,7 @@
         <v>94.477302693539272</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>

--- a/onderzoek_meta.xlsx
+++ b/onderzoek_meta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_4271AD50CF62512D295B6DB5CE110B54CD8AA6D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B2F070-D6CB-486C-999D-F7F2437A1243}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_4271AD50CF62512D295B6DB5CE110B54CD8AA6D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CDB8B6C-87FF-4F07-9416-C069EDA9D782}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2130" yWindow="2130" windowWidth="17280" windowHeight="8925" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SA" sheetId="1" r:id="rId1"/>
@@ -620,6 +620,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4614,6 +4625,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/onderzoek_meta.xlsx
+++ b/onderzoek_meta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_4271AD50CF62512D295B6DB5CE110B54CD8AA6D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CDB8B6C-87FF-4F07-9416-C069EDA9D782}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_4271AD50CF62512D295B6DB5CE110B54CD8AA6D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7FB0F7-3E3F-4CB2-AC02-E7D77788AD09}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2130" yWindow="2130" windowWidth="17280" windowHeight="8925" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SA" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,31 @@
     <sheet name="Alle combinaties" sheetId="3" r:id="rId3"/>
     <sheet name="Beste combinaties" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'Alle combinaties'!$M$2:$M$15</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Alle combinaties'!$N$2:$N$15</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Alle combinaties'!$M$2:$M$15</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Alle combinaties'!$N$2:$N$15</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="24">
   <si>
     <t>Snelheidsverhoging (%)</t>
   </si>
@@ -84,6 +103,18 @@
   <si>
     <t>M1 + M2 + M3</t>
   </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percentage verhoging </t>
+  </si>
 </sst>
 </file>
 
@@ -135,6 +166,2184 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA Improved'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA Improved'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA Improved'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>469.72222222222251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>224.6515151515153</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>284.777777777778</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>152.97435897435909</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>153.9444444444444</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C102-478B-B0F9-72F5C2ABA69D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA Improved'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA Improved'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA Improved'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>469.72222222222251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110.8787878787879</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>186.2222222222222</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>126.7948717948717</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>92.055555555555571</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C102-478B-B0F9-72F5C2ABA69D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SA Improved'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'SA Improved'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SA Improved'!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>469.72222222222251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>239.09848484848479</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150.82051282051259</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>91.444444444444457</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C102-478B-B0F9-72F5C2ABA69D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1306015199"/>
+        <c:axId val="1306012319"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1306015199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Snelheidsverandering</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" baseline="0"/>
+                  <a:t> per machine</a:t>
+                </a:r>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0&quot;%&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1306012319"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1306012319"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Totale penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1306015199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Alle combinaties'!$M$2:$M$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Alle combinaties'!$N$2:$N$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>214.27777777777771</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>123.69107744107741</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>128.2162733100233</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90.403651903651891</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74.863237746050245</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>59.155069930069928</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38.802566260899603</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.13803418803418</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.7445394112060768</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.0479797979798047</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.7407407407407369</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-414D-4CC6-83C0-9AF8E290A759}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1886157983"/>
+        <c:axId val="1886158463"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1886157983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1886158463"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1886158463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1886157983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>130175</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>434975</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{421C4FDF-E5C4-AE9E-AD54-7BF0A118C7D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>430893</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>102507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>49893</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>124279</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EE1F2D9-742D-942B-A83B-0421023F4B43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E53BA02-4F1A-4457-A855-1FAB75443900}" name="Table1" displayName="Table1" ref="A1:K1048576" totalsRowShown="0">
+  <autoFilter ref="A1:K1048576" xr:uid="{1E53BA02-4F1A-4457-A855-1FAB75443900}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K115">
+    <sortCondition ref="G1:G1048576"/>
+  </sortState>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{BD613ACF-CA1E-4D6F-9201-EB43E8F0FD7A}" name="Combinatie"/>
+    <tableColumn id="2" xr3:uid="{8A6918EB-7F3C-4326-A50C-3B2D8B88239F}" name="M1 (%)"/>
+    <tableColumn id="3" xr3:uid="{D1B13F5D-A486-4094-BCDF-0B077091C097}" name="M2 (%)"/>
+    <tableColumn id="4" xr3:uid="{B02400D7-35A6-4314-BFDA-4EA96CC019DA}" name="M3 (%)"/>
+    <tableColumn id="5" xr3:uid="{48AFB66C-2301-445C-84A0-1F0E50C13EBE}" name="Totale verhoging (%)"/>
+    <tableColumn id="6" xr3:uid="{A8E03290-8575-45B7-B110-11B424B2AC38}" name="Penalty SA"/>
+    <tableColumn id="7" xr3:uid="{AB558A79-68A5-41D7-8D0C-D989C7999C75}" name="Penalty SA Improved"/>
+    <tableColumn id="8" xr3:uid="{F8732039-8628-4530-B958-231CEC738938}" name="Rekentijd SA (s)"/>
+    <tableColumn id="9" xr3:uid="{D310801E-53CD-4A4D-A58E-3E97ACED92BA}" name="Rekentijd Improving (s)"/>
+    <tableColumn id="10" xr3:uid="{9FD206D2-AF13-4CA6-AD0D-CD8442A62B68}" name="Verbetering SA (%)"/>
+    <tableColumn id="11" xr3:uid="{5425F449-BCB4-4C48-963C-11EA595114D8}" name="Verbetering Improved (%)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,13 +2632,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +2652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -457,7 +2666,7 @@
         <v>469.72222222222251</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10</v>
       </c>
@@ -471,7 +2680,7 @@
         <v>239.09848484848479</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20</v>
       </c>
@@ -485,7 +2694,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>30</v>
       </c>
@@ -499,7 +2708,7 @@
         <v>150.82051282051259</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50</v>
       </c>
@@ -521,27 +2730,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -555,7 +2764,7 @@
         <v>469.72222222222251</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10</v>
       </c>
@@ -569,7 +2778,7 @@
         <v>239.09848484848479</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20</v>
       </c>
@@ -583,7 +2792,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>30</v>
       </c>
@@ -597,7 +2806,7 @@
         <v>150.82051282051259</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50</v>
       </c>
@@ -613,26 +2822,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K114"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N114"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="19.90625" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="9" max="9" width="22.26953125" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -666,564 +2877,670 @@
       <c r="K1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>469.72222222222251</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>469.72222222222251</v>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>3.972137599999769</v>
+      </c>
+      <c r="I2">
+        <v>1.857719999952678E-2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2">
+        <f>AVERAGEIF($E:$E,M2,$G:$G)</f>
+        <v>214.27777777777771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F3">
-        <v>208.81818181818181</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>208.81818181818181</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>4.6282578000000294</v>
+        <v>3.9148735999997371</v>
       </c>
       <c r="I3">
-        <v>2.0177600000351958E-2</v>
+        <v>2.0768399999724348E-2</v>
       </c>
       <c r="J3">
-        <v>55.544325573893907</v>
+        <v>100</v>
       </c>
       <c r="K3">
-        <v>55.544325573893907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M3">
+        <v>30</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N22" si="0">AVERAGEIF($E:$E,M3,$G:$G)</f>
+        <v>123.69107744107741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F4">
-        <v>85.555555555555571</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>85.555555555555571</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>4.1034015999994153</v>
+        <v>3.9443073000002191</v>
       </c>
       <c r="I4">
-        <v>1.9576599999709291E-2</v>
+        <v>2.631860000019515E-2</v>
       </c>
       <c r="J4">
-        <v>81.785925487877009</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>81.785925487877009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>128.2162733100233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>117.90909090909101</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>117.90909090909101</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>3.9910436999998642</v>
+        <v>4.0180141000000731</v>
       </c>
       <c r="I5">
-        <v>1.994620000004943E-2</v>
+        <v>2.048319999994419E-2</v>
       </c>
       <c r="J5">
-        <v>74.898123756787271</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>74.898123756787271</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>50</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>90.403651903651891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4.0554283999999834</v>
+      </c>
+      <c r="I6">
+        <v>2.019389999986743E-2</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="M6">
         <v>60</v>
       </c>
-      <c r="F6">
-        <v>202.72222222222209</v>
-      </c>
-      <c r="G6">
-        <v>58.666666666666593</v>
-      </c>
-      <c r="H6">
-        <v>4.2480731999994532</v>
-      </c>
-      <c r="I6">
-        <v>0.118058199999723</v>
-      </c>
-      <c r="J6">
-        <v>56.842105263157933</v>
-      </c>
-      <c r="K6">
-        <v>87.510348905972819</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>74.863237746050245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>20</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>244.03787878787861</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>244.03787878787861</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>4.4992655999994886</v>
+        <v>4.1072057999999743</v>
       </c>
       <c r="I7">
-        <v>2.10624999999709E-2</v>
+        <v>1.8968100000165581E-2</v>
       </c>
       <c r="J7">
-        <v>48.046341594538013</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>48.046341594538013</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>70</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>59.155069930069928</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>146.1388888888892</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>121.3055555555556</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>4.183994399999392</v>
+        <v>3.9559818999996419</v>
       </c>
       <c r="I8">
-        <v>7.8264799999487877E-2</v>
+        <v>2.4322199999915028E-2</v>
       </c>
       <c r="J8">
-        <v>68.888231815493739</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>74.175044352454165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <v>80</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>38.802566260899603</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>107.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>107.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>4.3737519000005696</v>
+        <v>3.944295799999963</v>
       </c>
       <c r="I9">
-        <v>2.2386200000255489E-2</v>
+        <v>1.9180199999937031E-2</v>
       </c>
       <c r="J9">
-        <v>77.149615612063869</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>77.149615612063869</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>90</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>23.13803418803418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E10">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F10">
-        <v>106.5555555555555</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>106.5555555555555</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>4.362242299999707</v>
+        <v>3.9793665000006508</v>
       </c>
       <c r="I10">
-        <v>1.961600000049657E-2</v>
+        <v>1.9116800000119841E-2</v>
       </c>
       <c r="J10">
-        <v>77.315198107628632</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>77.315198107628632</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>8.7445394112060768</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E11">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="F11">
-        <v>135.69230769230771</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>135.69230769230771</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>4.1897589999998672</v>
+        <v>3.7883300999992571</v>
       </c>
       <c r="I11">
-        <v>3.4568500000204949E-2</v>
+        <v>2.07457999995313E-2</v>
       </c>
       <c r="J11">
-        <v>71.112223081472067</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>71.112223081472067</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M11">
+        <v>110</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>9.0479797979798047</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F12">
-        <v>133.38461538461539</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>133.38461538461539</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>4.2353510000002643</v>
+        <v>4.1508929000001444</v>
       </c>
       <c r="I12">
-        <v>1.942630000030476E-2</v>
+        <v>1.9068300000071758E-2</v>
       </c>
       <c r="J12">
-        <v>71.603511804576272</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>71.603511804576272</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M12">
+        <v>120</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>22.307692307692299</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>22.307692307692299</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>4.2009401999994216</v>
+        <v>4.2487800999997489</v>
       </c>
       <c r="I13">
-        <v>1.9108700000288081E-2</v>
+        <v>2.3368500000287899E-2</v>
       </c>
       <c r="J13">
-        <v>95.250875676659234</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>95.250875676659234</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M13">
+        <v>130</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="0"/>
+        <v>4.7407407407407369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E14">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F14">
-        <v>23.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>23.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>3.8792739999998962</v>
+        <v>3.9818824000003592</v>
       </c>
       <c r="I14">
-        <v>1.9140000000334109E-2</v>
+        <v>2.06346000004487E-2</v>
       </c>
       <c r="J14">
-        <v>95.079834417504443</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>95.079834417504443</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M14">
+        <v>140</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>50</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E15">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F15">
-        <v>134.15656565656559</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>134.15656565656559</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>4.2015375999999378</v>
+        <v>3.8689269000005879</v>
       </c>
       <c r="I15">
-        <v>2.0861099999819999E-2</v>
+        <v>1.9010500000149481E-2</v>
       </c>
       <c r="J15">
-        <v>71.439169937100175</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>71.439169937100175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>150</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>50</v>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E16">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>3.990103299999646</v>
+        <v>3.995638899999904</v>
       </c>
       <c r="I16">
-        <v>2.1319999999832358E-2</v>
+        <v>1.9299399999908928E-2</v>
       </c>
       <c r="J16">
-        <v>91.05854523950326</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>91.05854523950326</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>50</v>
       </c>
       <c r="C17">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="F17">
-        <v>44.666666666666657</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>44.666666666666657</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>3.993315400000029</v>
+        <v>3.8717905000003161</v>
       </c>
       <c r="I17">
-        <v>2.0227699999850302E-2</v>
+        <v>1.9259200000306009E-2</v>
       </c>
       <c r="J17">
-        <v>90.490833826138399</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>90.490833826138399</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>50</v>
@@ -1232,10 +3549,10 @@
         <v>50</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1244,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>4.0180141000000731</v>
+        <v>3.922889599999507</v>
       </c>
       <c r="I18">
-        <v>2.048319999994419E-2</v>
+        <v>1.8806000000040509E-2</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -1256,497 +3573,497 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F19">
-        <v>215.1666666666666</v>
+        <v>20.424242424242411</v>
       </c>
       <c r="G19">
-        <v>215.1666666666666</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>3.847951900000226</v>
+        <v>3.5372360000001208</v>
       </c>
       <c r="I19">
-        <v>1.8512300000111281E-2</v>
+        <v>5.4736400000365393E-2</v>
       </c>
       <c r="J19">
-        <v>54.192785334121872</v>
+        <v>95.651846674909962</v>
       </c>
       <c r="K19">
-        <v>54.192785334121872</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>20</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F20">
-        <v>112.39393939393941</v>
+        <v>1.9999999999999929</v>
       </c>
       <c r="G20">
-        <v>108.5555555555556</v>
+        <v>1.9999999999999929</v>
       </c>
       <c r="H20">
-        <v>4.061018100000183</v>
+        <v>3.984966699999859</v>
       </c>
       <c r="I20">
-        <v>3.8376500000595122E-2</v>
+        <v>1.9689499999913099E-2</v>
       </c>
       <c r="J20">
-        <v>76.072254179882805</v>
+        <v>99.574216439976354</v>
       </c>
       <c r="K20">
-        <v>76.889414547604986</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>99.574216439976354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E21">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>148.4428904428905</v>
+        <v>5.7777777777778141</v>
       </c>
       <c r="G21">
-        <v>148.4428904428905</v>
+        <v>5.7777777777778141</v>
       </c>
       <c r="H21">
-        <v>4.1210962000004656</v>
+        <v>3.502641499999299</v>
       </c>
       <c r="I21">
-        <v>2.0321300000432529E-2</v>
+        <v>1.8207099999926871E-2</v>
       </c>
       <c r="J21">
-        <v>68.397728823512395</v>
+        <v>98.7699586043761</v>
       </c>
       <c r="K21">
-        <v>68.397728823512395</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>98.7699586043761</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D22">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E22">
+        <v>110</v>
+      </c>
+      <c r="F22">
+        <v>6.3333333333333428</v>
+      </c>
+      <c r="G22">
+        <v>6.3333333333333428</v>
+      </c>
+      <c r="H22">
+        <v>3.9361103999999609</v>
+      </c>
+      <c r="I22">
+        <v>1.978889999918465E-2</v>
+      </c>
+      <c r="J22">
+        <v>98.651685393258418</v>
+      </c>
+      <c r="K22">
+        <v>98.651685393258418</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>90</v>
+      </c>
+      <c r="F23">
+        <v>7.6581196581196451</v>
+      </c>
+      <c r="G23">
+        <v>7.6581196581196451</v>
+      </c>
+      <c r="H23">
+        <v>3.9196161999998371</v>
+      </c>
+      <c r="I23">
+        <v>2.041820000067673E-2</v>
+      </c>
+      <c r="J23">
+        <v>98.36964927443934</v>
+      </c>
+      <c r="K23">
+        <v>98.36964927443934</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>30</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+      <c r="E24">
+        <v>80</v>
+      </c>
+      <c r="F24">
+        <v>8.4722222222222143</v>
+      </c>
+      <c r="G24">
+        <v>8.4722222222222143</v>
+      </c>
+      <c r="H24">
+        <v>4.0083351000002949</v>
+      </c>
+      <c r="I24">
+        <v>2.1002700000281042E-2</v>
+      </c>
+      <c r="J24">
+        <v>98.196333530455348</v>
+      </c>
+      <c r="K24">
+        <v>98.196333530455348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>50</v>
+      </c>
+      <c r="E25">
+        <v>80</v>
+      </c>
+      <c r="F25">
+        <v>9.0909090909091006</v>
+      </c>
+      <c r="G25">
+        <v>9.0909090909091006</v>
+      </c>
+      <c r="H25">
+        <v>3.497335900000508</v>
+      </c>
+      <c r="I25">
+        <v>1.9003100000190901E-2</v>
+      </c>
+      <c r="J25">
+        <v>98.064620181710666</v>
+      </c>
+      <c r="K25">
+        <v>98.064620181710666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>30</v>
+      </c>
+      <c r="E26">
         <v>60</v>
       </c>
-      <c r="F22">
-        <v>149.60942760942751</v>
-      </c>
-      <c r="G22">
-        <v>149.60942760942751</v>
-      </c>
-      <c r="H22">
-        <v>3.9486461999995299</v>
-      </c>
-      <c r="I22">
-        <v>3.069669999968028E-2</v>
-      </c>
-      <c r="J22">
-        <v>68.149382649678373</v>
-      </c>
-      <c r="K22">
-        <v>68.149382649678373</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23">
-        <v>20</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>10</v>
-      </c>
-      <c r="E23">
-        <v>30</v>
-      </c>
-      <c r="F23">
-        <v>86.045454545454533</v>
-      </c>
-      <c r="G23">
-        <v>86.045454545454533</v>
-      </c>
-      <c r="H23">
-        <v>5.6185615999993388</v>
-      </c>
-      <c r="I23">
-        <v>3.5116000000016363E-2</v>
-      </c>
-      <c r="J23">
-        <v>81.681630019891429</v>
-      </c>
-      <c r="K23">
-        <v>81.681630019891429</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24">
-        <v>20</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
-      </c>
-      <c r="E24">
-        <v>40</v>
-      </c>
-      <c r="F24">
-        <v>125.3333333333334</v>
-      </c>
-      <c r="G24">
-        <v>125.3333333333334</v>
-      </c>
-      <c r="H24">
-        <v>4.1820728999991843</v>
-      </c>
-      <c r="I24">
-        <v>2.155510000011418E-2</v>
-      </c>
-      <c r="J24">
-        <v>73.317563571850968</v>
-      </c>
-      <c r="K24">
-        <v>73.317563571850968</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25">
-        <v>20</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>30</v>
-      </c>
-      <c r="E25">
-        <v>50</v>
-      </c>
-      <c r="F25">
-        <v>64.666666666666657</v>
-      </c>
-      <c r="G25">
-        <v>64.666666666666657</v>
-      </c>
-      <c r="H25">
-        <v>4.8810282999993433</v>
-      </c>
-      <c r="I25">
-        <v>2.143009999963397E-2</v>
-      </c>
-      <c r="J25">
-        <v>86.232998225901852</v>
-      </c>
-      <c r="K25">
-        <v>86.232998225901852</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26">
-        <v>20</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>50</v>
-      </c>
-      <c r="E26">
+      <c r="F26">
+        <v>10.5</v>
+      </c>
+      <c r="G26">
+        <v>10.5</v>
+      </c>
+      <c r="H26">
+        <v>3.474173300000075</v>
+      </c>
+      <c r="I26">
+        <v>1.809610000054818E-2</v>
+      </c>
+      <c r="J26">
+        <v>97.764636309875812</v>
+      </c>
+      <c r="K26">
+        <v>97.764636309875812</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27">
         <v>70</v>
       </c>
-      <c r="F26">
-        <v>29.000000000000011</v>
-      </c>
-      <c r="G26">
-        <v>29.000000000000011</v>
-      </c>
-      <c r="H26">
-        <v>3.9872342999997268</v>
-      </c>
-      <c r="I26">
-        <v>2.2359700000379231E-2</v>
-      </c>
-      <c r="J26">
-        <v>93.82613837965701</v>
-      </c>
-      <c r="K26">
-        <v>93.82613837965701</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27">
-        <v>30</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
-      <c r="E27">
-        <v>40</v>
-      </c>
       <c r="F27">
-        <v>69.842268842268766</v>
+        <v>10.5</v>
       </c>
       <c r="G27">
-        <v>69.842268842268766</v>
+        <v>10.5</v>
       </c>
       <c r="H27">
-        <v>4.1112206999996488</v>
+        <v>3.9087201000002101</v>
       </c>
       <c r="I27">
-        <v>2.1588800000245101E-2</v>
+        <v>2.1134100000381299E-2</v>
       </c>
       <c r="J27">
-        <v>85.131155066104824</v>
+        <v>97.764636309875812</v>
       </c>
       <c r="K27">
-        <v>85.131155066104824</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>97.764636309875812</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D28">
         <v>20</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>53.666666666666657</v>
+        <v>13.999999999999989</v>
       </c>
       <c r="G28">
-        <v>23.000000000000011</v>
+        <v>13.999999999999989</v>
       </c>
       <c r="H28">
-        <v>4.416650899999695</v>
+        <v>4.1409766999995554</v>
       </c>
       <c r="I28">
-        <v>4.1859299999487121E-2</v>
+        <v>1.9991399999526038E-2</v>
       </c>
       <c r="J28">
-        <v>88.574807806031956</v>
+        <v>97.01951507983442</v>
       </c>
       <c r="K28">
-        <v>95.103489059727977</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>97.01951507983442</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B29">
         <v>30</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E29">
+        <v>130</v>
+      </c>
+      <c r="F29">
+        <v>14.222222222222211</v>
+      </c>
+      <c r="G29">
+        <v>14.222222222222211</v>
+      </c>
+      <c r="H29">
+        <v>3.9516855000001669</v>
+      </c>
+      <c r="I29">
+        <v>2.112200000010489E-2</v>
+      </c>
+      <c r="J29">
+        <v>96.972205795387339</v>
+      </c>
+      <c r="K29">
+        <v>96.972205795387339</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>50</v>
+      </c>
+      <c r="E30">
+        <v>110</v>
+      </c>
+      <c r="F30">
+        <v>19.954545454545471</v>
+      </c>
+      <c r="G30">
+        <v>19.954545454545471</v>
+      </c>
+      <c r="H30">
+        <v>3.5206756999996291</v>
+      </c>
+      <c r="I30">
+        <v>1.7916300000251791E-2</v>
+      </c>
+      <c r="J30">
+        <v>95.751841298854885</v>
+      </c>
+      <c r="K30">
+        <v>95.751841298854885</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>50</v>
+      </c>
+      <c r="F31">
+        <v>20.151515151515159</v>
+      </c>
+      <c r="G31">
+        <v>20.151515151515159</v>
+      </c>
+      <c r="H31">
+        <v>3.479792099999941</v>
+      </c>
+      <c r="I31">
+        <v>1.743639999949664E-2</v>
+      </c>
+      <c r="J31">
+        <v>95.709908069458635</v>
+      </c>
+      <c r="K31">
+        <v>95.709908069458635</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32">
+        <v>30</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
         <v>60</v>
       </c>
-      <c r="F29">
-        <v>77.743589743589666</v>
-      </c>
-      <c r="G29">
-        <v>77.743589743589666</v>
-      </c>
-      <c r="H29">
-        <v>4.2043776999998954</v>
-      </c>
-      <c r="I29">
-        <v>2.087690000007569E-2</v>
-      </c>
-      <c r="J29">
-        <v>83.449028794977963</v>
-      </c>
-      <c r="K29">
-        <v>83.449028794977963</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30">
-        <v>30</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>50</v>
-      </c>
-      <c r="E30">
-        <v>80</v>
-      </c>
-      <c r="F30">
-        <v>29.111111111111128</v>
-      </c>
-      <c r="G30">
-        <v>29.111111111111128</v>
-      </c>
-      <c r="H30">
-        <v>4.5102600999998694</v>
-      </c>
-      <c r="I30">
-        <v>2.7868600000147129E-2</v>
-      </c>
-      <c r="J30">
-        <v>93.802483737433477</v>
-      </c>
-      <c r="K30">
-        <v>93.802483737433477</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31">
-        <v>50</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
-        <v>10</v>
-      </c>
-      <c r="E31">
-        <v>60</v>
-      </c>
-      <c r="F31">
-        <v>60.500000000000092</v>
-      </c>
-      <c r="G31">
-        <v>60.500000000000007</v>
-      </c>
-      <c r="H31">
-        <v>3.9550684000005281</v>
-      </c>
-      <c r="I31">
-        <v>3.8394100000004983E-2</v>
-      </c>
-      <c r="J31">
-        <v>87.120047309284431</v>
-      </c>
-      <c r="K31">
-        <v>87.120047309284459</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32">
-        <v>50</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>20</v>
-      </c>
-      <c r="E32">
-        <v>70</v>
-      </c>
       <c r="F32">
-        <v>55.5</v>
+        <v>22.307692307692299</v>
       </c>
       <c r="G32">
-        <v>55.5</v>
+        <v>22.307692307692299</v>
       </c>
       <c r="H32">
-        <v>3.7430899999999379</v>
+        <v>4.2009401999994216</v>
       </c>
       <c r="I32">
-        <v>1.835459999983868E-2</v>
+        <v>1.9108700000288081E-2</v>
       </c>
       <c r="J32">
-        <v>88.184506209343596</v>
+        <v>95.250875676659234</v>
       </c>
       <c r="K32">
-        <v>88.184506209343596</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>95.250875676659234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1781,295 +4098,295 @@
         <v>95.130782877678215</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <v>50</v>
+      </c>
+      <c r="E34">
+        <v>90</v>
+      </c>
+      <c r="F34">
+        <v>22.999999999999989</v>
+      </c>
+      <c r="G34">
+        <v>22.999999999999989</v>
+      </c>
+      <c r="H34">
+        <v>3.6014774000004759</v>
+      </c>
+      <c r="I34">
+        <v>1.7759500000465781E-2</v>
+      </c>
+      <c r="J34">
+        <v>95.103489059727977</v>
+      </c>
+      <c r="K34">
+        <v>95.103489059727977</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>50</v>
+      </c>
+      <c r="C35">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>90</v>
+      </c>
+      <c r="F35">
+        <v>22.999999999999989</v>
+      </c>
+      <c r="G35">
+        <v>22.999999999999989</v>
+      </c>
+      <c r="H35">
+        <v>3.9741444000001138</v>
+      </c>
+      <c r="I35">
+        <v>1.9729399999960151E-2</v>
+      </c>
+      <c r="J35">
+        <v>95.103489059727977</v>
+      </c>
+      <c r="K35">
+        <v>95.103489059727977</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>17</v>
       </c>
-      <c r="B34">
-        <v>50</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>50</v>
-      </c>
-      <c r="E34">
+      <c r="B36">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>20</v>
+      </c>
+      <c r="E36">
+        <v>50</v>
+      </c>
+      <c r="F36">
+        <v>53.666666666666657</v>
+      </c>
+      <c r="G36">
+        <v>23.000000000000011</v>
+      </c>
+      <c r="H36">
+        <v>4.416650899999695</v>
+      </c>
+      <c r="I36">
+        <v>4.1859299999487121E-2</v>
+      </c>
+      <c r="J36">
+        <v>88.574807806031956</v>
+      </c>
+      <c r="K36">
+        <v>95.103489059727977</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>80</v>
+      </c>
+      <c r="F37">
+        <v>23.111111111111111</v>
+      </c>
+      <c r="G37">
+        <v>23.111111111111111</v>
+      </c>
+      <c r="H37">
+        <v>3.8792739999998962</v>
+      </c>
+      <c r="I37">
+        <v>1.9140000000334109E-2</v>
+      </c>
+      <c r="J37">
+        <v>95.079834417504443</v>
+      </c>
+      <c r="K37">
+        <v>95.079834417504443</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>50</v>
+      </c>
+      <c r="E38">
+        <v>90</v>
+      </c>
+      <c r="F38">
+        <v>26.888888888888889</v>
+      </c>
+      <c r="G38">
+        <v>26.888888888888889</v>
+      </c>
+      <c r="H38">
+        <v>4.5372509999997419</v>
+      </c>
+      <c r="I38">
+        <v>1.9391699999687258E-2</v>
+      </c>
+      <c r="J38">
+        <v>94.275576581904204</v>
+      </c>
+      <c r="K38">
+        <v>94.275576581904204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39">
+        <v>50</v>
+      </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+      <c r="D39">
+        <v>20</v>
+      </c>
+      <c r="E39">
+        <v>80</v>
+      </c>
+      <c r="F39">
+        <v>27.999999999999989</v>
+      </c>
+      <c r="G39">
+        <v>27.999999999999989</v>
+      </c>
+      <c r="H39">
+        <v>3.814709700000094</v>
+      </c>
+      <c r="I39">
+        <v>2.1254399999634192E-2</v>
+      </c>
+      <c r="J39">
+        <v>94.03903015966884</v>
+      </c>
+      <c r="K39">
+        <v>94.03903015966884</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40">
+        <v>50</v>
+      </c>
+      <c r="C40">
+        <v>50</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>110</v>
+      </c>
+      <c r="F40">
+        <v>28.000000000000011</v>
+      </c>
+      <c r="G40">
+        <v>28.000000000000011</v>
+      </c>
+      <c r="H40">
+        <v>3.9098359999998138</v>
+      </c>
+      <c r="I40">
+        <v>1.9866300000103369E-2</v>
+      </c>
+      <c r="J40">
+        <v>94.03903015966884</v>
+      </c>
+      <c r="K40">
+        <v>94.03903015966884</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>50</v>
+      </c>
+      <c r="E41">
         <v>100</v>
       </c>
-      <c r="F34">
-        <v>30</v>
-      </c>
-      <c r="G34">
+      <c r="F41">
+        <v>30</v>
+      </c>
+      <c r="G41">
         <v>28.000000000000011</v>
       </c>
-      <c r="H34">
+      <c r="H41">
         <v>3.6105177000008548</v>
       </c>
-      <c r="I34">
+      <c r="I41">
         <v>3.6346099999718717E-2</v>
       </c>
-      <c r="J34">
+      <c r="J41">
         <v>93.61324659964518</v>
       </c>
-      <c r="K34">
+      <c r="K41">
         <v>94.03903015966884</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35">
-        <v>10</v>
-      </c>
-      <c r="E35">
-        <v>20</v>
-      </c>
-      <c r="F35">
-        <v>218.84848484848479</v>
-      </c>
-      <c r="G35">
-        <v>218.84848484848479</v>
-      </c>
-      <c r="H35">
-        <v>4.1878240999994887</v>
-      </c>
-      <c r="I35">
-        <v>2.338760000020557E-2</v>
-      </c>
-      <c r="J35">
-        <v>53.408956507714677</v>
-      </c>
-      <c r="K35">
-        <v>53.408956507714677</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>10</v>
-      </c>
-      <c r="D36">
-        <v>20</v>
-      </c>
-      <c r="E36">
-        <v>30</v>
-      </c>
-      <c r="F36">
-        <v>98.111111111111171</v>
-      </c>
-      <c r="G36">
-        <v>85.481481481481524</v>
-      </c>
-      <c r="H36">
-        <v>3.9809378999998439</v>
-      </c>
-      <c r="I36">
-        <v>3.6504400000012538E-2</v>
-      </c>
-      <c r="J36">
-        <v>79.112950916617379</v>
-      </c>
-      <c r="K36">
-        <v>81.801695249359355</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>30</v>
-      </c>
-      <c r="E37">
-        <v>40</v>
-      </c>
-      <c r="F37">
-        <v>213.31857031857029</v>
-      </c>
-      <c r="G37">
-        <v>213.31857031857029</v>
-      </c>
-      <c r="H37">
-        <v>3.6303936000003891</v>
-      </c>
-      <c r="I37">
-        <v>1.8807899999956131E-2</v>
-      </c>
-      <c r="J37">
-        <v>54.58622985530144</v>
-      </c>
-      <c r="K37">
-        <v>54.58622985530144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>50</v>
-      </c>
-      <c r="E38">
-        <v>60</v>
-      </c>
-      <c r="F38">
-        <v>31.37037037037037</v>
-      </c>
-      <c r="G38">
-        <v>31.37037037037037</v>
-      </c>
-      <c r="H38">
-        <v>3.8364185999998881</v>
-      </c>
-      <c r="I38">
-        <v>2.39940999999817E-2</v>
-      </c>
-      <c r="J38">
-        <v>93.321506012221562</v>
-      </c>
-      <c r="K38">
-        <v>93.321506012221562</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>20</v>
-      </c>
-      <c r="D39">
-        <v>10</v>
-      </c>
-      <c r="E39">
-        <v>30</v>
-      </c>
-      <c r="F39">
-        <v>112.8888888888888</v>
-      </c>
-      <c r="G39">
-        <v>112.8888888888888</v>
-      </c>
-      <c r="H39">
-        <v>4.6199765000001207</v>
-      </c>
-      <c r="I39">
-        <v>2.104830000007496E-2</v>
-      </c>
-      <c r="J39">
-        <v>75.966883500887079</v>
-      </c>
-      <c r="K39">
-        <v>75.966883500887079</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>20</v>
-      </c>
-      <c r="D40">
-        <v>20</v>
-      </c>
-      <c r="E40">
-        <v>40</v>
-      </c>
-      <c r="F40">
-        <v>99.2083333333334</v>
-      </c>
-      <c r="G40">
-        <v>99.2083333333334</v>
-      </c>
-      <c r="H40">
-        <v>3.923431400000482</v>
-      </c>
-      <c r="I40">
-        <v>2.0994399999835881E-2</v>
-      </c>
-      <c r="J40">
-        <v>78.879361324659968</v>
-      </c>
-      <c r="K40">
-        <v>78.879361324659968</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>20</v>
-      </c>
-      <c r="D41">
-        <v>30</v>
-      </c>
-      <c r="E41">
-        <v>50</v>
-      </c>
-      <c r="F41">
-        <v>99.541666666666657</v>
-      </c>
-      <c r="G41">
-        <v>92.666666666666657</v>
-      </c>
-      <c r="H41">
-        <v>4.0409733999995296</v>
-      </c>
-      <c r="I41">
-        <v>4.1794499999923573E-2</v>
-      </c>
-      <c r="J41">
-        <v>78.808397397989367</v>
-      </c>
-      <c r="K41">
-        <v>80.272028385570692</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>50</v>
@@ -2078,65 +4395,65 @@
         <v>70</v>
       </c>
       <c r="F42">
-        <v>167.9305555555556</v>
+        <v>29.000000000000011</v>
       </c>
       <c r="G42">
-        <v>167.9305555555556</v>
+        <v>29.000000000000011</v>
       </c>
       <c r="H42">
-        <v>4.0252071999993859</v>
+        <v>3.9872342999997268</v>
       </c>
       <c r="I42">
-        <v>1.989549999962037E-2</v>
+        <v>2.2359700000379231E-2</v>
       </c>
       <c r="J42">
-        <v>64.248965109402747</v>
+        <v>93.82613837965701</v>
       </c>
       <c r="K42">
-        <v>64.248965109402747</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.82613837965701</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C43">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E43">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F43">
-        <v>84.311965811965649</v>
+        <v>29.111111111111128</v>
       </c>
       <c r="G43">
-        <v>79.388888888888829</v>
+        <v>29.111111111111128</v>
       </c>
       <c r="H43">
-        <v>3.5748615000002251</v>
+        <v>4.5102600999998694</v>
       </c>
       <c r="I43">
-        <v>3.6530399999719521E-2</v>
+        <v>2.7868600000147129E-2</v>
       </c>
       <c r="J43">
-        <v>82.050675521994307</v>
+        <v>93.802483737433477</v>
       </c>
       <c r="K43">
-        <v>83.09875813128329</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.802483737433477</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C44">
         <v>30</v>
@@ -2145,33 +4462,33 @@
         <v>20</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F44">
-        <v>154.86894586894579</v>
+        <v>30.01994301994306</v>
       </c>
       <c r="G44">
-        <v>154.86894586894579</v>
+        <v>30.01994301994306</v>
       </c>
       <c r="H44">
-        <v>3.4936676000006628</v>
+        <v>4.1468601000005947</v>
       </c>
       <c r="I44">
-        <v>1.8082600000525421E-2</v>
+        <v>2.2106500000518281E-2</v>
       </c>
       <c r="J44">
-        <v>67.029674445404808</v>
+        <v>93.609000894630697</v>
       </c>
       <c r="K44">
-        <v>67.029674445404808</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.609000894630697</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C45">
         <v>30</v>
@@ -2180,28 +4497,28 @@
         <v>30</v>
       </c>
       <c r="E45">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F45">
-        <v>72</v>
+        <v>30.658119658119642</v>
       </c>
       <c r="G45">
-        <v>72</v>
+        <v>30.658119658119642</v>
       </c>
       <c r="H45">
-        <v>3.5013971999997011</v>
+        <v>5.0306337000001804</v>
       </c>
       <c r="I45">
-        <v>1.7830499999945459E-2</v>
+        <v>2.3371600000245959E-2</v>
       </c>
       <c r="J45">
-        <v>84.67179183914844</v>
+        <v>93.473138334167317</v>
       </c>
       <c r="K45">
-        <v>84.67179183914844</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.473138334167317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2209,104 +4526,104 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D46">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E46">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F46">
-        <v>39</v>
+        <v>30.7777777777778</v>
       </c>
       <c r="G46">
-        <v>39</v>
+        <v>30.7777777777778</v>
       </c>
       <c r="H46">
-        <v>3.5141132999997349</v>
+        <v>3.4916069000000789</v>
       </c>
       <c r="I46">
-        <v>1.8055200000162589E-2</v>
+        <v>1.7859900000075871E-2</v>
       </c>
       <c r="J46">
-        <v>91.697220579538737</v>
+        <v>93.447664104080417</v>
       </c>
       <c r="K46">
-        <v>91.697220579538737</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.447664104080417</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C47">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E47">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F47">
-        <v>134.30303030303031</v>
+        <v>30.7777777777778</v>
       </c>
       <c r="G47">
-        <v>134.30303030303031</v>
+        <v>30.7777777777778</v>
       </c>
       <c r="H47">
-        <v>3.5424430999992178</v>
+        <v>3.9768692000006922</v>
       </c>
       <c r="I47">
-        <v>1.9187500000043659E-2</v>
+        <v>2.1058100000118429E-2</v>
       </c>
       <c r="J47">
-        <v>71.407988817805517</v>
+        <v>93.447664104080417</v>
       </c>
       <c r="K47">
-        <v>71.407988817805517</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.447664104080417</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C48">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E48">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F48">
-        <v>30.7777777777778</v>
+        <v>30.923076923076881</v>
       </c>
       <c r="G48">
-        <v>30.7777777777778</v>
+        <v>30.923076923076881</v>
       </c>
       <c r="H48">
-        <v>3.4916069000000789</v>
+        <v>3.9905171000000341</v>
       </c>
       <c r="I48">
-        <v>1.7859900000075871E-2</v>
+        <v>1.9395899999835819E-2</v>
       </c>
       <c r="J48">
-        <v>93.447664104080417</v>
+        <v>93.416731110403504</v>
       </c>
       <c r="K48">
-        <v>93.447664104080417</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.416731110403504</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -2314,279 +4631,279 @@
         <v>0</v>
       </c>
       <c r="C49">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E49">
+        <v>60</v>
+      </c>
+      <c r="F49">
+        <v>31.37037037037037</v>
+      </c>
+      <c r="G49">
+        <v>31.37037037037037</v>
+      </c>
+      <c r="H49">
+        <v>3.8364185999998881</v>
+      </c>
+      <c r="I49">
+        <v>2.39940999999817E-2</v>
+      </c>
+      <c r="J49">
+        <v>93.321506012221562</v>
+      </c>
+      <c r="K49">
+        <v>93.321506012221562</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50">
+        <v>30</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+      <c r="E50">
+        <v>70</v>
+      </c>
+      <c r="F50">
+        <v>38.119658119658091</v>
+      </c>
+      <c r="G50">
+        <v>38.119658119658091</v>
+      </c>
+      <c r="H50">
+        <v>4.1372503000002334</v>
+      </c>
+      <c r="I50">
+        <v>2.1268299999974261E-2</v>
+      </c>
+      <c r="J50">
+        <v>91.884638129463696</v>
+      </c>
+      <c r="K50">
+        <v>91.884638129463696</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>30</v>
+      </c>
+      <c r="D51">
+        <v>50</v>
+      </c>
+      <c r="E51">
         <v>80</v>
       </c>
-      <c r="F49">
-        <v>93</v>
-      </c>
-      <c r="G49">
-        <v>93</v>
-      </c>
-      <c r="H49">
-        <v>3.536945699999706</v>
-      </c>
-      <c r="I49">
-        <v>1.7935400000169469E-2</v>
-      </c>
-      <c r="J49">
-        <v>80.201064458900078</v>
-      </c>
-      <c r="K49">
-        <v>80.201064458900078</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>50</v>
-      </c>
-      <c r="D50">
-        <v>50</v>
-      </c>
-      <c r="E50">
-        <v>100</v>
-      </c>
-      <c r="F50">
-        <v>5.7777777777778141</v>
-      </c>
-      <c r="G50">
-        <v>5.7777777777778141</v>
-      </c>
-      <c r="H50">
-        <v>3.502641499999299</v>
-      </c>
-      <c r="I50">
-        <v>1.8207099999926871E-2</v>
-      </c>
-      <c r="J50">
-        <v>98.7699586043761</v>
-      </c>
-      <c r="K50">
-        <v>98.7699586043761</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51">
-        <v>10</v>
-      </c>
-      <c r="C51">
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <v>10</v>
-      </c>
-      <c r="E51">
-        <v>30</v>
-      </c>
       <c r="F51">
-        <v>143.2727272727272</v>
+        <v>39</v>
       </c>
       <c r="G51">
-        <v>143.2727272727272</v>
+        <v>39</v>
       </c>
       <c r="H51">
-        <v>3.5190886999998838</v>
+        <v>3.5141132999997349</v>
       </c>
       <c r="I51">
-        <v>1.825900000039837E-2</v>
+        <v>1.8055200000162589E-2</v>
       </c>
       <c r="J51">
-        <v>69.498414063760066</v>
+        <v>91.697220579538737</v>
       </c>
       <c r="K51">
-        <v>69.498414063760066</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>91.697220579538737</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>19</v>
       </c>
       <c r="B52">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D52">
         <v>20</v>
       </c>
       <c r="E52">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F52">
-        <v>89.818181818181813</v>
+        <v>40.205128205128183</v>
       </c>
       <c r="G52">
-        <v>89.818181818181813</v>
+        <v>40.205128205128183</v>
       </c>
       <c r="H52">
-        <v>3.4791805999993808</v>
+        <v>3.943428100000347</v>
       </c>
       <c r="I52">
-        <v>1.9657499999993892E-2</v>
+        <v>1.987319999989268E-2</v>
       </c>
       <c r="J52">
-        <v>80.87844739530135</v>
+        <v>91.440658690806544</v>
       </c>
       <c r="K52">
-        <v>80.87844739530135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <v>91.440658690806544</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>19</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C53">
         <v>10</v>
       </c>
       <c r="D53">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F53">
-        <v>20.151515151515159</v>
+        <v>41.636363636363633</v>
       </c>
       <c r="G53">
-        <v>20.151515151515159</v>
+        <v>41.636363636363633</v>
       </c>
       <c r="H53">
-        <v>3.479792099999941</v>
+        <v>3.5217345000000928</v>
       </c>
       <c r="I53">
-        <v>1.743639999949664E-2</v>
+        <v>1.8088699999680099E-2</v>
       </c>
       <c r="J53">
-        <v>95.709908069458635</v>
+        <v>91.135960432234825</v>
       </c>
       <c r="K53">
-        <v>95.709908069458635</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+        <v>91.135960432234825</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D54">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>70</v>
       </c>
       <c r="F54">
-        <v>46.636363636363633</v>
+        <v>42</v>
       </c>
       <c r="G54">
-        <v>46.636363636363633</v>
+        <v>42</v>
       </c>
       <c r="H54">
-        <v>3.6104016999997839</v>
+        <v>3.990103299999646</v>
       </c>
       <c r="I54">
-        <v>1.8011400000432332E-2</v>
+        <v>2.1319999999832358E-2</v>
       </c>
       <c r="J54">
-        <v>90.071501532175702</v>
+        <v>91.05854523950326</v>
       </c>
       <c r="K54">
-        <v>90.071501532175702</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>91.05854523950326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B55">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C55">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F55">
-        <v>159.03282828282821</v>
+        <v>44.666666666666657</v>
       </c>
       <c r="G55">
-        <v>159.03282828282821</v>
+        <v>44.666666666666657</v>
       </c>
       <c r="H55">
-        <v>3.494073700000627</v>
+        <v>3.993315400000029</v>
       </c>
       <c r="I55">
-        <v>1.7639000000599481E-2</v>
+        <v>2.0227699999850302E-2</v>
       </c>
       <c r="J55">
-        <v>66.143218106553448</v>
+        <v>90.490833826138399</v>
       </c>
       <c r="K55">
-        <v>66.143218106553448</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>90.490833826138399</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>19</v>
       </c>
       <c r="B56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F56">
-        <v>113.1127946127948</v>
+        <v>60.868686868686993</v>
       </c>
       <c r="G56">
-        <v>62.193602693602799</v>
+        <v>45.535353535353551</v>
       </c>
       <c r="H56">
-        <v>3.5241519999999582</v>
+        <v>3.8606432999995381</v>
       </c>
       <c r="I56">
-        <v>5.6320599999708072E-2</v>
+        <v>5.7237399999394263E-2</v>
       </c>
       <c r="J56">
-        <v>75.919215812769906</v>
+        <v>87.041556905542691</v>
       </c>
       <c r="K56">
-        <v>86.759493217210533</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+        <v>90.30589753239073</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -2594,34 +4911,34 @@
         <v>10</v>
       </c>
       <c r="C57">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D57">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E57">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F57">
-        <v>56.18181818181818</v>
+        <v>46.636363636363633</v>
       </c>
       <c r="G57">
-        <v>56.18181818181818</v>
+        <v>46.636363636363633</v>
       </c>
       <c r="H57">
-        <v>3.4969858000004019</v>
+        <v>3.6104016999997839</v>
       </c>
       <c r="I57">
-        <v>1.812040000004345E-2</v>
+        <v>1.8011400000432332E-2</v>
       </c>
       <c r="J57">
-        <v>88.039352722971884</v>
+        <v>90.071501532175702</v>
       </c>
       <c r="K57">
-        <v>88.039352722971884</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+        <v>90.071501532175702</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -2629,39 +4946,39 @@
         <v>10</v>
       </c>
       <c r="C58">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D58">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E58">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F58">
-        <v>9.0909090909091006</v>
+        <v>48.181818181818201</v>
       </c>
       <c r="G58">
-        <v>9.0909090909091006</v>
+        <v>48.181818181818201</v>
       </c>
       <c r="H58">
-        <v>3.497335900000508</v>
+        <v>3.4988756000002472</v>
       </c>
       <c r="I58">
-        <v>1.9003100000190901E-2</v>
+        <v>1.8497000000024851E-2</v>
       </c>
       <c r="J58">
-        <v>98.064620181710666</v>
+        <v>89.742486963066497</v>
       </c>
       <c r="K58">
-        <v>98.064620181710666</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+        <v>89.742486963066497</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>19</v>
       </c>
       <c r="B59">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C59">
         <v>30</v>
@@ -2670,36 +4987,36 @@
         <v>10</v>
       </c>
       <c r="E59">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F59">
-        <v>149.80069930069931</v>
+        <v>50.262626262626227</v>
       </c>
       <c r="G59">
-        <v>149.80069930069931</v>
+        <v>50.262626262626227</v>
       </c>
       <c r="H59">
-        <v>3.5013198000006009</v>
+        <v>3.9774756999995589</v>
       </c>
       <c r="I59">
-        <v>1.83139000000665E-2</v>
+        <v>2.121729999998934E-2</v>
       </c>
       <c r="J59">
-        <v>68.108662478857653</v>
+        <v>89.299500026880295</v>
       </c>
       <c r="K59">
-        <v>68.108662478857653</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+        <v>89.299500026880295</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
       <c r="B60">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C60">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D60">
         <v>20</v>
@@ -2708,60 +5025,60 @@
         <v>60</v>
       </c>
       <c r="F60">
-        <v>65.841750841750894</v>
+        <v>51.447811447811489</v>
       </c>
       <c r="G60">
-        <v>65.841750841750894</v>
+        <v>51.447811447811489</v>
       </c>
       <c r="H60">
-        <v>3.5324833000004219</v>
+        <v>4.1718098999999711</v>
       </c>
       <c r="I60">
-        <v>1.811219999945024E-2</v>
+        <v>3.987559999950463E-2</v>
       </c>
       <c r="J60">
-        <v>85.982832464204435</v>
+        <v>89.047183843162543</v>
       </c>
       <c r="K60">
-        <v>85.982832464204435</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <v>89.047183843162543</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B61">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C61">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E61">
         <v>70</v>
       </c>
       <c r="F61">
-        <v>48.181818181818201</v>
+        <v>55.5</v>
       </c>
       <c r="G61">
-        <v>48.181818181818201</v>
+        <v>55.5</v>
       </c>
       <c r="H61">
-        <v>3.4988756000002472</v>
+        <v>3.7430899999999379</v>
       </c>
       <c r="I61">
-        <v>1.8497000000024851E-2</v>
+        <v>1.835459999983868E-2</v>
       </c>
       <c r="J61">
-        <v>89.742486963066497</v>
+        <v>88.184506209343596</v>
       </c>
       <c r="K61">
-        <v>89.742486963066497</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <v>88.184506209343596</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -2769,36 +5086,36 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D62">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E62">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F62">
-        <v>22.999999999999989</v>
+        <v>56.18181818181818</v>
       </c>
       <c r="G62">
-        <v>22.999999999999989</v>
+        <v>56.18181818181818</v>
       </c>
       <c r="H62">
-        <v>3.6014774000004759</v>
+        <v>3.4969858000004019</v>
       </c>
       <c r="I62">
-        <v>1.7759500000465781E-2</v>
+        <v>1.812040000004345E-2</v>
       </c>
       <c r="J62">
-        <v>95.103489059727977</v>
+        <v>88.039352722971884</v>
       </c>
       <c r="K62">
-        <v>95.103489059727977</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+        <v>88.039352722971884</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -2807,66 +5124,66 @@
         <v>50</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F63">
-        <v>101.8383838383839</v>
+        <v>202.72222222222209</v>
       </c>
       <c r="G63">
-        <v>101.8383838383839</v>
+        <v>58.666666666666593</v>
       </c>
       <c r="H63">
-        <v>3.4914296999995709</v>
+        <v>4.2480731999994532</v>
       </c>
       <c r="I63">
-        <v>1.8451799999638752E-2</v>
+        <v>0.118058199999723</v>
       </c>
       <c r="J63">
-        <v>78.319445191118774</v>
+        <v>56.842105263157933</v>
       </c>
       <c r="K63">
-        <v>78.319445191118774</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>87.510348905972819</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B64">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C64">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E64">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F64">
-        <v>64.36363636363636</v>
+        <v>60.500000000000092</v>
       </c>
       <c r="G64">
-        <v>64.36363636363636</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="H64">
-        <v>3.5330020000001241</v>
+        <v>3.9550684000005281</v>
       </c>
       <c r="I64">
-        <v>1.7616499999348889E-2</v>
+        <v>3.8394100000004983E-2</v>
       </c>
       <c r="J64">
-        <v>86.297510886511489</v>
+        <v>87.120047309284431</v>
       </c>
       <c r="K64">
-        <v>86.297510886511489</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>87.120047309284459</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -2874,34 +5191,34 @@
         <v>10</v>
       </c>
       <c r="C65">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D65">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E65">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F65">
-        <v>20.424242424242411</v>
+        <v>113.1127946127948</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>62.193602693602799</v>
       </c>
       <c r="H65">
-        <v>3.5372360000001208</v>
+        <v>3.5241519999999582</v>
       </c>
       <c r="I65">
-        <v>5.4736400000365393E-2</v>
+        <v>5.6320599999708072E-2</v>
       </c>
       <c r="J65">
-        <v>95.651846674909962</v>
+        <v>75.919215812769906</v>
       </c>
       <c r="K65">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+        <v>86.759493217210533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -2912,101 +5229,101 @@
         <v>50</v>
       </c>
       <c r="D66">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E66">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F66">
-        <v>19.954545454545471</v>
+        <v>64.36363636363636</v>
       </c>
       <c r="G66">
-        <v>19.954545454545471</v>
+        <v>64.36363636363636</v>
       </c>
       <c r="H66">
-        <v>3.5206756999996291</v>
+        <v>3.5330020000001241</v>
       </c>
       <c r="I66">
-        <v>1.7916300000251791E-2</v>
+        <v>1.7616499999348889E-2</v>
       </c>
       <c r="J66">
-        <v>95.751841298854885</v>
+        <v>86.297510886511489</v>
       </c>
       <c r="K66">
-        <v>95.751841298854885</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>86.297510886511489</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B67">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E67">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F67">
-        <v>179.30303030303031</v>
+        <v>64.666666666666657</v>
       </c>
       <c r="G67">
-        <v>179.30303030303031</v>
+        <v>64.666666666666657</v>
       </c>
       <c r="H67">
-        <v>3.4697272000003072</v>
+        <v>4.8810282999993433</v>
       </c>
       <c r="I67">
-        <v>1.755119999961607E-2</v>
+        <v>2.143009999963397E-2</v>
       </c>
       <c r="J67">
-        <v>61.827858717273301</v>
+        <v>86.232998225901852</v>
       </c>
       <c r="K67">
-        <v>61.827858717273301</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+        <v>86.232998225901852</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>19</v>
       </c>
       <c r="B68">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D68">
         <v>20</v>
       </c>
       <c r="E68">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F68">
-        <v>188.58585858585829</v>
+        <v>65.841750841750894</v>
       </c>
       <c r="G68">
-        <v>128.55555555555549</v>
+        <v>65.841750841750894</v>
       </c>
       <c r="H68">
-        <v>3.5069681000004489</v>
+        <v>3.5324833000004219</v>
       </c>
       <c r="I68">
-        <v>7.1378900000127032E-2</v>
+        <v>1.811219999945024E-2</v>
       </c>
       <c r="J68">
-        <v>59.851620880597913</v>
+        <v>85.982832464204435</v>
       </c>
       <c r="K68">
-        <v>72.631578947368439</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+        <v>85.982832464204435</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -3014,139 +5331,139 @@
         <v>20</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D69">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E69">
+        <v>50</v>
+      </c>
+      <c r="F69">
+        <v>66.868686868686851</v>
+      </c>
+      <c r="G69">
+        <v>66.868686868686851</v>
+      </c>
+      <c r="H69">
+        <v>3.5057818000004768</v>
+      </c>
+      <c r="I69">
+        <v>1.8047499999738651E-2</v>
+      </c>
+      <c r="J69">
+        <v>85.764206225471767</v>
+      </c>
+      <c r="K69">
+        <v>85.764206225471767</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70">
+        <v>30</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70">
+        <v>40</v>
+      </c>
+      <c r="F70">
+        <v>69.842268842268766</v>
+      </c>
+      <c r="G70">
+        <v>69.842268842268766</v>
+      </c>
+      <c r="H70">
+        <v>4.1112206999996488</v>
+      </c>
+      <c r="I70">
+        <v>2.1588800000245101E-2</v>
+      </c>
+      <c r="J70">
+        <v>85.131155066104824</v>
+      </c>
+      <c r="K70">
+        <v>85.131155066104824</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71">
         <v>60</v>
       </c>
-      <c r="F69">
-        <v>10.5</v>
-      </c>
-      <c r="G69">
-        <v>10.5</v>
-      </c>
-      <c r="H69">
-        <v>3.474173300000075</v>
-      </c>
-      <c r="I69">
-        <v>1.809610000054818E-2</v>
-      </c>
-      <c r="J69">
-        <v>97.764636309875812</v>
-      </c>
-      <c r="K69">
-        <v>97.764636309875812</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70">
-        <v>20</v>
-      </c>
-      <c r="C70">
-        <v>10</v>
-      </c>
-      <c r="D70">
-        <v>50</v>
-      </c>
-      <c r="E70">
-        <v>80</v>
-      </c>
-      <c r="F70">
-        <v>41.636363636363633</v>
-      </c>
-      <c r="G70">
-        <v>41.636363636363633</v>
-      </c>
-      <c r="H70">
-        <v>3.5217345000000928</v>
-      </c>
-      <c r="I70">
-        <v>1.8088699999680099E-2</v>
-      </c>
-      <c r="J70">
-        <v>91.135960432234825</v>
-      </c>
-      <c r="K70">
-        <v>91.135960432234825</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>19</v>
-      </c>
-      <c r="B71">
-        <v>20</v>
-      </c>
-      <c r="C71">
-        <v>20</v>
-      </c>
-      <c r="D71">
-        <v>10</v>
-      </c>
-      <c r="E71">
-        <v>50</v>
-      </c>
       <c r="F71">
-        <v>66.868686868686851</v>
+        <v>72</v>
       </c>
       <c r="G71">
-        <v>66.868686868686851</v>
+        <v>72</v>
       </c>
       <c r="H71">
-        <v>3.5057818000004768</v>
+        <v>3.5013971999997011</v>
       </c>
       <c r="I71">
-        <v>1.8047499999738651E-2</v>
+        <v>1.7830499999945459E-2</v>
       </c>
       <c r="J71">
-        <v>85.764206225471767</v>
+        <v>84.67179183914844</v>
       </c>
       <c r="K71">
-        <v>85.764206225471767</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+        <v>84.67179183914844</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>19</v>
       </c>
       <c r="B72">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C72">
         <v>20</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E72">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F72">
-        <v>119.6666666666667</v>
+        <v>72.501262626262658</v>
       </c>
       <c r="G72">
-        <v>119.6666666666667</v>
+        <v>72.501262626262658</v>
       </c>
       <c r="H72">
-        <v>3.6754449999998542</v>
+        <v>3.6675903000004841</v>
       </c>
       <c r="I72">
-        <v>1.9039400000110621E-2</v>
+        <v>1.8354600000748181E-2</v>
       </c>
       <c r="J72">
-        <v>74.523950325251349</v>
+        <v>84.565077146389996</v>
       </c>
       <c r="K72">
-        <v>74.523950325251349</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+        <v>84.565077146389996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -3154,74 +5471,74 @@
         <v>20</v>
       </c>
       <c r="C73">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D73">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E73">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F73">
-        <v>10.5</v>
+        <v>73.757575757575751</v>
       </c>
       <c r="G73">
-        <v>10.5</v>
+        <v>73.757575757575751</v>
       </c>
       <c r="H73">
-        <v>3.9087201000002101</v>
+        <v>3.8558122000004</v>
       </c>
       <c r="I73">
-        <v>2.1134100000381299E-2</v>
+        <v>1.9364900000255151E-2</v>
       </c>
       <c r="J73">
-        <v>97.764636309875812</v>
+        <v>84.297618407612504</v>
       </c>
       <c r="K73">
-        <v>97.764636309875812</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+        <v>84.297618407612504</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B74">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C74">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E74">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F74">
-        <v>26.888888888888889</v>
+        <v>77.743589743589666</v>
       </c>
       <c r="G74">
-        <v>26.888888888888889</v>
+        <v>77.743589743589666</v>
       </c>
       <c r="H74">
-        <v>4.5372509999997419</v>
+        <v>4.2043776999998954</v>
       </c>
       <c r="I74">
-        <v>1.9391699999687258E-2</v>
+        <v>2.087690000007569E-2</v>
       </c>
       <c r="J74">
-        <v>94.275576581904204</v>
+        <v>83.449028794977963</v>
       </c>
       <c r="K74">
-        <v>94.275576581904204</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83.449028794977963</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B75">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C75">
         <v>30</v>
@@ -3230,1414 +5547,1412 @@
         <v>10</v>
       </c>
       <c r="E75">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F75">
-        <v>73.757575757575751</v>
+        <v>84.311965811965649</v>
       </c>
       <c r="G75">
-        <v>73.757575757575751</v>
+        <v>79.388888888888829</v>
       </c>
       <c r="H75">
-        <v>3.8558122000004</v>
+        <v>3.5748615000002251</v>
       </c>
       <c r="I75">
-        <v>1.9364900000255151E-2</v>
+        <v>3.6530399999719521E-2</v>
       </c>
       <c r="J75">
-        <v>84.297618407612504</v>
+        <v>82.050675521994307</v>
       </c>
       <c r="K75">
-        <v>84.297618407612504</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83.09875813128329</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>19</v>
       </c>
       <c r="B76">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C76">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E76">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F76">
-        <v>40.205128205128183</v>
+        <v>79.758838383838423</v>
       </c>
       <c r="G76">
-        <v>40.205128205128183</v>
+        <v>79.758838383838423</v>
       </c>
       <c r="H76">
-        <v>3.943428100000347</v>
+        <v>3.9555580000005648</v>
       </c>
       <c r="I76">
-        <v>1.987319999989268E-2</v>
+        <v>2.0067400000698399E-2</v>
       </c>
       <c r="J76">
-        <v>91.440658690806544</v>
+        <v>83.019998924788979</v>
       </c>
       <c r="K76">
-        <v>91.440658690806544</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83.019998924788979</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>19</v>
       </c>
       <c r="B77">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C77">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D77">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E77">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F77">
-        <v>30.658119658119642</v>
+        <v>81.353535353535307</v>
       </c>
       <c r="G77">
-        <v>30.658119658119642</v>
+        <v>81.353535353535307</v>
       </c>
       <c r="H77">
-        <v>5.0306337000001804</v>
+        <v>4.2061039999998684</v>
       </c>
       <c r="I77">
-        <v>2.3371600000245959E-2</v>
+        <v>2.208900000005087E-2</v>
       </c>
       <c r="J77">
-        <v>93.473138334167317</v>
+        <v>82.68050104833074</v>
       </c>
       <c r="K77">
-        <v>93.473138334167317</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+        <v>82.68050104833074</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B78">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D78">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E78">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>98.111111111111171</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>85.481481481481524</v>
       </c>
       <c r="H78">
-        <v>4.0554283999999834</v>
+        <v>3.9809378999998439</v>
       </c>
       <c r="I78">
-        <v>2.019389999986743E-2</v>
+        <v>3.6504400000012538E-2</v>
       </c>
       <c r="J78">
-        <v>100</v>
+        <v>79.112950916617379</v>
       </c>
       <c r="K78">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+        <v>81.801695249359355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B79">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F79">
-        <v>60.868686868686993</v>
+        <v>85.555555555555571</v>
       </c>
       <c r="G79">
-        <v>45.535353535353551</v>
+        <v>85.555555555555571</v>
       </c>
       <c r="H79">
-        <v>3.8606432999995381</v>
+        <v>4.1034015999994153</v>
       </c>
       <c r="I79">
-        <v>5.7237399999394263E-2</v>
+        <v>1.9576599999709291E-2</v>
       </c>
       <c r="J79">
-        <v>87.041556905542691</v>
+        <v>81.785925487877009</v>
       </c>
       <c r="K79">
-        <v>90.30589753239073</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+        <v>81.785925487877009</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B80">
         <v>20</v>
       </c>
       <c r="C80">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E80">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F80">
-        <v>148.83333333333329</v>
+        <v>86.045454545454533</v>
       </c>
       <c r="G80">
-        <v>148.83333333333329</v>
+        <v>86.045454545454533</v>
       </c>
       <c r="H80">
-        <v>4.2901738000000478</v>
+        <v>5.6185615999993388</v>
       </c>
       <c r="I80">
-        <v>2.2331600000143229E-2</v>
+        <v>3.5116000000016363E-2</v>
       </c>
       <c r="J80">
-        <v>68.314606741573044</v>
+        <v>81.681630019891429</v>
       </c>
       <c r="K80">
-        <v>68.314606741573044</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+        <v>81.681630019891429</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>19</v>
       </c>
       <c r="B81">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C81">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D81">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E81">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>89.04040404040397</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>89.04040404040397</v>
       </c>
       <c r="H81">
-        <v>4.1072057999999743</v>
+        <v>3.9191383000006681</v>
       </c>
       <c r="I81">
-        <v>1.8968100000165581E-2</v>
+        <v>2.1134800000254469E-2</v>
       </c>
       <c r="J81">
-        <v>100</v>
+        <v>81.044029890866113</v>
       </c>
       <c r="K81">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+        <v>81.044029890866113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>19</v>
       </c>
       <c r="B82">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C82">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D82">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E82">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>89.818181818181813</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>89.818181818181813</v>
       </c>
       <c r="H82">
-        <v>4.2487800999997489</v>
+        <v>3.4791805999993808</v>
       </c>
       <c r="I82">
-        <v>2.3368500000287899E-2</v>
+        <v>1.9657499999993892E-2</v>
       </c>
       <c r="J82">
-        <v>100</v>
+        <v>80.87844739530135</v>
       </c>
       <c r="K82">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+        <v>80.87844739530135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B83">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E83">
         <v>50</v>
       </c>
       <c r="F83">
-        <v>81.353535353535307</v>
+        <v>99.541666666666657</v>
       </c>
       <c r="G83">
-        <v>81.353535353535307</v>
+        <v>92.666666666666657</v>
       </c>
       <c r="H83">
-        <v>4.2061039999998684</v>
+        <v>4.0409733999995296</v>
       </c>
       <c r="I83">
-        <v>2.208900000005087E-2</v>
+        <v>4.1794499999923573E-2</v>
       </c>
       <c r="J83">
-        <v>82.68050104833074</v>
+        <v>78.808397397989367</v>
       </c>
       <c r="K83">
-        <v>82.68050104833074</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+        <v>80.272028385570692</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B84">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D84">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E84">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F84">
-        <v>51.447811447811489</v>
+        <v>93</v>
       </c>
       <c r="G84">
-        <v>51.447811447811489</v>
+        <v>93</v>
       </c>
       <c r="H84">
-        <v>4.1718098999999711</v>
+        <v>3.536945699999706</v>
       </c>
       <c r="I84">
-        <v>3.987559999950463E-2</v>
+        <v>1.7935400000169469E-2</v>
       </c>
       <c r="J84">
-        <v>89.047183843162543</v>
+        <v>80.201064458900078</v>
       </c>
       <c r="K84">
-        <v>89.047183843162543</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+        <v>80.201064458900078</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B85">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D85">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E85">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F85">
-        <v>38.119658119658091</v>
+        <v>99.2083333333334</v>
       </c>
       <c r="G85">
-        <v>38.119658119658091</v>
+        <v>99.2083333333334</v>
       </c>
       <c r="H85">
-        <v>4.1372503000002334</v>
+        <v>3.923431400000482</v>
       </c>
       <c r="I85">
-        <v>2.1268299999974261E-2</v>
+        <v>2.0994399999835881E-2</v>
       </c>
       <c r="J85">
-        <v>91.884638129463696</v>
+        <v>78.879361324659968</v>
       </c>
       <c r="K85">
-        <v>91.884638129463696</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+        <v>78.879361324659968</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>19</v>
       </c>
       <c r="B86">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D86">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E86">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>101.8383838383839</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>101.8383838383839</v>
       </c>
       <c r="H86">
-        <v>3.972137599999769</v>
+        <v>3.4914296999995709</v>
       </c>
       <c r="I86">
-        <v>1.857719999952678E-2</v>
+        <v>1.8451799999638752E-2</v>
       </c>
       <c r="J86">
-        <v>100</v>
+        <v>78.319445191118774</v>
       </c>
       <c r="K86">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+        <v>78.319445191118774</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B87">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C87">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F87">
-        <v>79.758838383838423</v>
+        <v>106.5555555555555</v>
       </c>
       <c r="G87">
-        <v>79.758838383838423</v>
+        <v>106.5555555555555</v>
       </c>
       <c r="H87">
-        <v>3.9555580000005648</v>
+        <v>4.362242299999707</v>
       </c>
       <c r="I87">
-        <v>2.0067400000698399E-2</v>
+        <v>1.961600000049657E-2</v>
       </c>
       <c r="J87">
-        <v>83.019998924788979</v>
+        <v>77.315198107628632</v>
       </c>
       <c r="K87">
-        <v>83.019998924788979</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+        <v>77.315198107628632</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B88">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C88">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D88">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F88">
-        <v>30.7777777777778</v>
+        <v>107.3333333333333</v>
       </c>
       <c r="G88">
-        <v>30.7777777777778</v>
+        <v>107.3333333333333</v>
       </c>
       <c r="H88">
-        <v>3.9768692000006922</v>
+        <v>4.3737519000005696</v>
       </c>
       <c r="I88">
-        <v>2.1058100000118429E-2</v>
+        <v>2.2386200000255489E-2</v>
       </c>
       <c r="J88">
-        <v>93.447664104080417</v>
+        <v>77.149615612063869</v>
       </c>
       <c r="K88">
-        <v>93.447664104080417</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+        <v>77.149615612063869</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B89">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E89">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F89">
-        <v>8.4722222222222143</v>
+        <v>112.39393939393941</v>
       </c>
       <c r="G89">
-        <v>8.4722222222222143</v>
+        <v>108.5555555555556</v>
       </c>
       <c r="H89">
-        <v>4.0083351000002949</v>
+        <v>4.061018100000183</v>
       </c>
       <c r="I89">
-        <v>2.1002700000281042E-2</v>
+        <v>3.8376500000595122E-2</v>
       </c>
       <c r="J89">
-        <v>98.196333530455348</v>
+        <v>76.072254179882805</v>
       </c>
       <c r="K89">
-        <v>98.196333530455348</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+        <v>76.889414547604986</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B90">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>20</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E90">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>112.8888888888888</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>112.8888888888888</v>
       </c>
       <c r="H90">
-        <v>3.9559818999996419</v>
+        <v>4.6199765000001207</v>
       </c>
       <c r="I90">
-        <v>2.4322199999915028E-2</v>
+        <v>2.104830000007496E-2</v>
       </c>
       <c r="J90">
-        <v>100</v>
+        <v>75.966883500887079</v>
       </c>
       <c r="K90">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+        <v>75.966883500887079</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B91">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C91">
         <v>30</v>
       </c>
       <c r="D91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F91">
-        <v>50.262626262626227</v>
+        <v>117.90909090909101</v>
       </c>
       <c r="G91">
-        <v>50.262626262626227</v>
+        <v>117.90909090909101</v>
       </c>
       <c r="H91">
-        <v>3.9774756999995589</v>
+        <v>3.9910436999998642</v>
       </c>
       <c r="I91">
-        <v>2.121729999998934E-2</v>
+        <v>1.994620000004943E-2</v>
       </c>
       <c r="J91">
-        <v>89.299500026880295</v>
+        <v>74.898123756787271</v>
       </c>
       <c r="K91">
-        <v>89.299500026880295</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+        <v>74.898123756787271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>19</v>
       </c>
       <c r="B92">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C92">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D92">
         <v>20</v>
       </c>
       <c r="E92">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F92">
-        <v>30.01994301994306</v>
+        <v>119.6666666666667</v>
       </c>
       <c r="G92">
-        <v>30.01994301994306</v>
+        <v>119.6666666666667</v>
       </c>
       <c r="H92">
-        <v>4.1468601000005947</v>
+        <v>3.6754449999998542</v>
       </c>
       <c r="I92">
-        <v>2.2106500000518281E-2</v>
+        <v>1.9039400000110621E-2</v>
       </c>
       <c r="J92">
-        <v>93.609000894630697</v>
+        <v>74.523950325251349</v>
       </c>
       <c r="K92">
-        <v>93.609000894630697</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+        <v>74.523950325251349</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B93">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C93">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D93">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>146.1388888888892</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>121.3055555555556</v>
       </c>
       <c r="H93">
-        <v>3.9148735999997371</v>
+        <v>4.183994399999392</v>
       </c>
       <c r="I93">
-        <v>2.0768399999724348E-2</v>
+        <v>7.8264799999487877E-2</v>
       </c>
       <c r="J93">
-        <v>100</v>
+        <v>68.888231815493739</v>
       </c>
       <c r="K93">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+        <v>74.175044352454165</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B94">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C94">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E94">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>125.3333333333334</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>125.3333333333334</v>
       </c>
       <c r="H94">
-        <v>3.9793665000006508</v>
+        <v>4.1820728999991843</v>
       </c>
       <c r="I94">
-        <v>1.9116800000119841E-2</v>
+        <v>2.155510000011418E-2</v>
       </c>
       <c r="J94">
-        <v>100</v>
+        <v>73.317563571850968</v>
       </c>
       <c r="K94">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+        <v>73.317563571850968</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>19</v>
       </c>
       <c r="B95">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C95">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E95">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>188.58585858585829</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>128.55555555555549</v>
       </c>
       <c r="H95">
-        <v>3.9443073000002191</v>
+        <v>3.5069681000004489</v>
       </c>
       <c r="I95">
-        <v>2.631860000019515E-2</v>
+        <v>7.1378900000127032E-2</v>
       </c>
       <c r="J95">
-        <v>100</v>
+        <v>59.851620880597913</v>
       </c>
       <c r="K95">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+        <v>72.631578947368439</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B96">
         <v>30</v>
       </c>
       <c r="C96">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D96">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>133.38461538461539</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>133.38461538461539</v>
       </c>
       <c r="H96">
-        <v>3.944295799999963</v>
+        <v>4.2353510000002643</v>
       </c>
       <c r="I96">
-        <v>1.9180199999937031E-2</v>
+        <v>1.942630000030476E-2</v>
       </c>
       <c r="J96">
-        <v>100</v>
+        <v>71.603511804576272</v>
       </c>
       <c r="K96">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+        <v>71.603511804576272</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B97">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C97">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D97">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="F97">
-        <v>6.3333333333333428</v>
+        <v>134.15656565656559</v>
       </c>
       <c r="G97">
-        <v>6.3333333333333428</v>
+        <v>134.15656565656559</v>
       </c>
       <c r="H97">
-        <v>3.9361103999999609</v>
+        <v>4.2015375999999378</v>
       </c>
       <c r="I97">
-        <v>1.978889999918465E-2</v>
+        <v>2.0861099999819999E-2</v>
       </c>
       <c r="J97">
-        <v>98.651685393258418</v>
+        <v>71.439169937100175</v>
       </c>
       <c r="K97">
-        <v>98.651685393258418</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+        <v>71.439169937100175</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B98">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C98">
         <v>50</v>
       </c>
       <c r="D98">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E98">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F98">
-        <v>14.222222222222211</v>
+        <v>134.30303030303031</v>
       </c>
       <c r="G98">
-        <v>14.222222222222211</v>
+        <v>134.30303030303031</v>
       </c>
       <c r="H98">
-        <v>3.9516855000001669</v>
+        <v>3.5424430999992178</v>
       </c>
       <c r="I98">
-        <v>2.112200000010489E-2</v>
+        <v>1.9187500000043659E-2</v>
       </c>
       <c r="J98">
-        <v>96.972205795387339</v>
+        <v>71.407988817805517</v>
       </c>
       <c r="K98">
-        <v>96.972205795387339</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+        <v>71.407988817805517</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B99">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C99">
         <v>10</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F99">
-        <v>89.04040404040397</v>
+        <v>135.69230769230771</v>
       </c>
       <c r="G99">
-        <v>89.04040404040397</v>
+        <v>135.69230769230771</v>
       </c>
       <c r="H99">
-        <v>3.9191383000006681</v>
+        <v>4.1897589999998672</v>
       </c>
       <c r="I99">
-        <v>2.1134800000254469E-2</v>
+        <v>3.4568500000204949E-2</v>
       </c>
       <c r="J99">
-        <v>81.044029890866113</v>
+        <v>71.112223081472067</v>
       </c>
       <c r="K99">
-        <v>81.044029890866113</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+        <v>71.112223081472067</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>19</v>
       </c>
       <c r="B100">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C100">
         <v>10</v>
       </c>
       <c r="D100">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E100">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F100">
-        <v>27.999999999999989</v>
+        <v>143.2727272727272</v>
       </c>
       <c r="G100">
-        <v>27.999999999999989</v>
+        <v>143.2727272727272</v>
       </c>
       <c r="H100">
-        <v>3.814709700000094</v>
+        <v>3.5190886999998838</v>
       </c>
       <c r="I100">
-        <v>2.1254399999634192E-2</v>
+        <v>1.825900000039837E-2</v>
       </c>
       <c r="J100">
-        <v>94.03903015966884</v>
+        <v>69.498414063760066</v>
       </c>
       <c r="K100">
-        <v>94.03903015966884</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+        <v>69.498414063760066</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B101">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>30</v>
       </c>
       <c r="E101">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F101">
-        <v>7.6581196581196451</v>
+        <v>148.4428904428905</v>
       </c>
       <c r="G101">
-        <v>7.6581196581196451</v>
+        <v>148.4428904428905</v>
       </c>
       <c r="H101">
-        <v>3.9196161999998371</v>
+        <v>4.1210962000004656</v>
       </c>
       <c r="I101">
-        <v>2.041820000067673E-2</v>
+        <v>2.0321300000432529E-2</v>
       </c>
       <c r="J101">
-        <v>98.36964927443934</v>
+        <v>68.397728823512395</v>
       </c>
       <c r="K101">
-        <v>98.36964927443934</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+        <v>68.397728823512395</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>19</v>
       </c>
       <c r="B102">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D102">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E102">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>148.83333333333329</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>148.83333333333329</v>
       </c>
       <c r="H102">
-        <v>3.7883300999992571</v>
+        <v>4.2901738000000478</v>
       </c>
       <c r="I102">
-        <v>2.07457999995313E-2</v>
+        <v>2.2331600000143229E-2</v>
       </c>
       <c r="J102">
-        <v>100</v>
+        <v>68.314606741573044</v>
       </c>
       <c r="K102">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+        <v>68.314606741573044</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B103">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C103">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E103">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F103">
-        <v>72.501262626262658</v>
+        <v>149.60942760942751</v>
       </c>
       <c r="G103">
-        <v>72.501262626262658</v>
+        <v>149.60942760942751</v>
       </c>
       <c r="H103">
-        <v>3.6675903000004841</v>
+        <v>3.9486461999995299</v>
       </c>
       <c r="I103">
-        <v>1.8354600000748181E-2</v>
+        <v>3.069669999968028E-2</v>
       </c>
       <c r="J103">
-        <v>84.565077146389996</v>
+        <v>68.149382649678373</v>
       </c>
       <c r="K103">
-        <v>84.565077146389996</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+        <v>68.149382649678373</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>19</v>
       </c>
       <c r="B104">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C104">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D104">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E104">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F104">
-        <v>1.9999999999999929</v>
+        <v>149.80069930069931</v>
       </c>
       <c r="G104">
-        <v>1.9999999999999929</v>
+        <v>149.80069930069931</v>
       </c>
       <c r="H104">
-        <v>3.984966699999859</v>
+        <v>3.5013198000006009</v>
       </c>
       <c r="I104">
-        <v>1.9689499999913099E-2</v>
+        <v>1.83139000000665E-2</v>
       </c>
       <c r="J104">
-        <v>99.574216439976354</v>
+        <v>68.108662478857653</v>
       </c>
       <c r="K104">
-        <v>99.574216439976354</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+        <v>68.108662478857653</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B105">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D105">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E105">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F105">
-        <v>30.923076923076881</v>
+        <v>154.86894586894579</v>
       </c>
       <c r="G105">
-        <v>30.923076923076881</v>
+        <v>154.86894586894579</v>
       </c>
       <c r="H105">
-        <v>3.9905171000000341</v>
+        <v>3.4936676000006628</v>
       </c>
       <c r="I105">
-        <v>1.9395899999835819E-2</v>
+        <v>1.8082600000525421E-2</v>
       </c>
       <c r="J105">
-        <v>93.416731110403504</v>
+        <v>67.029674445404808</v>
       </c>
       <c r="K105">
-        <v>93.416731110403504</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+        <v>67.029674445404808</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>19</v>
       </c>
       <c r="B106">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C106">
         <v>20</v>
       </c>
       <c r="D106">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E106">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>159.03282828282821</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>159.03282828282821</v>
       </c>
       <c r="H106">
-        <v>3.9818824000003592</v>
+        <v>3.494073700000627</v>
       </c>
       <c r="I106">
-        <v>2.06346000004487E-2</v>
+        <v>1.7639000000599481E-2</v>
       </c>
       <c r="J106">
-        <v>100</v>
+        <v>66.143218106553448</v>
       </c>
       <c r="K106">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+        <v>66.143218106553448</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B107">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E107">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F107">
-        <v>22.999999999999989</v>
+        <v>167.9305555555556</v>
       </c>
       <c r="G107">
-        <v>22.999999999999989</v>
+        <v>167.9305555555556</v>
       </c>
       <c r="H107">
-        <v>3.9741444000001138</v>
+        <v>4.0252071999993859</v>
       </c>
       <c r="I107">
-        <v>1.9729399999960151E-2</v>
+        <v>1.989549999962037E-2</v>
       </c>
       <c r="J107">
-        <v>95.103489059727977</v>
+        <v>64.248965109402747</v>
       </c>
       <c r="K107">
-        <v>95.103489059727977</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+        <v>64.248965109402747</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>19</v>
       </c>
       <c r="B108">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C108">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D108">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E108">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F108">
-        <v>13.999999999999989</v>
+        <v>179.30303030303031</v>
       </c>
       <c r="G108">
-        <v>13.999999999999989</v>
+        <v>179.30303030303031</v>
       </c>
       <c r="H108">
-        <v>4.1409766999995554</v>
+        <v>3.4697272000003072</v>
       </c>
       <c r="I108">
-        <v>1.9991399999526038E-2</v>
+        <v>1.755119999961607E-2</v>
       </c>
       <c r="J108">
-        <v>97.01951507983442</v>
+        <v>61.827858717273301</v>
       </c>
       <c r="K108">
-        <v>97.01951507983442</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+        <v>61.827858717273301</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B109">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C109">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D109">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E109">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>208.81818181818181</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>208.81818181818181</v>
       </c>
       <c r="H109">
-        <v>4.1508929000001444</v>
+        <v>4.6282578000000294</v>
       </c>
       <c r="I109">
-        <v>1.9068300000071758E-2</v>
+        <v>2.0177600000351958E-2</v>
       </c>
       <c r="J109">
-        <v>100</v>
+        <v>55.544325573893907</v>
       </c>
       <c r="K109">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+        <v>55.544325573893907</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B110">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D110">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E110">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>213.31857031857029</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>213.31857031857029</v>
       </c>
       <c r="H110">
-        <v>3.995638899999904</v>
+        <v>3.6303936000003891</v>
       </c>
       <c r="I110">
-        <v>1.9299399999908928E-2</v>
+        <v>1.8807899999956131E-2</v>
       </c>
       <c r="J110">
-        <v>100</v>
+        <v>54.58622985530144</v>
       </c>
       <c r="K110">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+        <v>54.58622985530144</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B111">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C111">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>10</v>
       </c>
       <c r="E111">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="F111">
-        <v>28.000000000000011</v>
+        <v>215.1666666666666</v>
       </c>
       <c r="G111">
-        <v>28.000000000000011</v>
+        <v>215.1666666666666</v>
       </c>
       <c r="H111">
-        <v>3.9098359999998138</v>
+        <v>3.847951900000226</v>
       </c>
       <c r="I111">
-        <v>1.9866300000103369E-2</v>
+        <v>1.8512300000111281E-2</v>
       </c>
       <c r="J111">
-        <v>94.03903015966884</v>
+        <v>54.192785334121872</v>
       </c>
       <c r="K111">
-        <v>94.03903015966884</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+        <v>54.192785334121872</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B112">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D112">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E112">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>218.84848484848479</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>218.84848484848479</v>
       </c>
       <c r="H112">
-        <v>3.8689269000005879</v>
+        <v>4.1878240999994887</v>
       </c>
       <c r="I112">
-        <v>1.9010500000149481E-2</v>
+        <v>2.338760000020557E-2</v>
       </c>
       <c r="J112">
-        <v>100</v>
+        <v>53.408956507714677</v>
       </c>
       <c r="K112">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+        <v>53.408956507714677</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B113">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C113">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D113">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E113">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>244.03787878787861</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>244.03787878787861</v>
       </c>
       <c r="H113">
-        <v>3.8717905000003161</v>
+        <v>4.4992655999994886</v>
       </c>
       <c r="I113">
-        <v>1.9259200000306009E-2</v>
+        <v>2.10624999999709E-2</v>
       </c>
       <c r="J113">
-        <v>100</v>
+        <v>48.046341594538013</v>
       </c>
       <c r="K113">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+        <v>48.046341594538013</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B114">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>469.72222222222251</v>
       </c>
       <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
-        <v>3.922889599999507</v>
-      </c>
-      <c r="I114">
-        <v>1.8806000000040509E-2</v>
+        <v>469.72222222222251</v>
       </c>
       <c r="J114">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -4672,7 +6987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -4707,7 +7022,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4742,7 +7057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4777,7 +7092,7 @@
         <v>98.7699586043761</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -4812,7 +7127,7 @@
         <v>95.130782877678215</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>

--- a/onderzoek_meta.xlsx
+++ b/onderzoek_meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_4271AD50CF62512D295B6DB5CE110B54CD8AA6D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7FB0F7-3E3F-4CB2-AC02-E7D77788AD09}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_4271AD50CF62512D295B6DB5CE110B54CD8AA6D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C51032F8-AE0F-4DA6-B76B-0E5EBF6E0039}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -825,7 +825,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -904,40 +904,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>214.27777777777771</c:v>
+                  <c:v>208.81818181818181</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123.69107744107741</c:v>
+                  <c:v>85.481481481481524</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>128.2162733100233</c:v>
+                  <c:v>69.842268842268766</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90.403651903651891</c:v>
+                  <c:v>20.151515151515159</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>74.863237746050245</c:v>
+                  <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>59.155069930069928</c:v>
+                  <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38.802566260899603</c:v>
+                  <c:v>8.4722222222222143</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>23.13803418803418</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.7445394112060768</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.0479797979798047</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.7407407407407369</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -970,6 +970,8 @@
         <c:axId val="1886157983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="140"/>
+          <c:min val="20"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -987,7 +989,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Totale verhoging (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0&quot;%&quot;" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1027,6 +1084,7 @@
         <c:crossAx val="1886158463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:minorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1886158463"/>
@@ -1049,6 +1107,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Ttotale penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2286,16 +2399,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>430893</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>141515</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>102507</xdr:rowOff>
+      <xdr:rowOff>106136</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>49893</xdr:colOff>
+      <xdr:colOff>368301</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>124279</xdr:rowOff>
+      <xdr:rowOff>127908</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2919,8 +3032,8 @@
         <v>20</v>
       </c>
       <c r="N2">
-        <f>AVERAGEIF($E:$E,M2,$G:$G)</f>
-        <v>214.27777777777771</v>
+        <f>_xlfn.MINIFS($G$2:$G$1000,$E$2:$E$1000,M2)</f>
+        <v>208.81818181818181</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -2961,8 +3074,8 @@
         <v>30</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N22" si="0">AVERAGEIF($E:$E,M3,$G:$G)</f>
-        <v>123.69107744107741</v>
+        <f t="shared" ref="N3:N15" si="0">_xlfn.MINIFS($G$2:$G$1000,$E$2:$E$1000,M3)</f>
+        <v>85.481481481481524</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -3004,7 +3117,7 @@
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>128.2162733100233</v>
+        <v>69.842268842268766</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -3046,7 +3159,7 @@
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>90.403651903651891</v>
+        <v>20.151515151515159</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -3088,7 +3201,7 @@
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>74.863237746050245</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -3130,7 +3243,7 @@
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>59.155069930069928</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -3172,7 +3285,7 @@
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>38.802566260899603</v>
+        <v>8.4722222222222143</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -3214,7 +3327,7 @@
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>23.13803418803418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -3256,7 +3369,7 @@
       </c>
       <c r="N10">
         <f t="shared" si="0"/>
-        <v>8.7445394112060768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -3298,7 +3411,7 @@
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
-        <v>9.0479797979798047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -3382,7 +3495,7 @@
       </c>
       <c r="N13">
         <f t="shared" si="0"/>
-        <v>4.7407407407407369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -3423,6 +3536,7 @@
         <v>140</v>
       </c>
       <c r="N14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
